--- a/papertrader/tracker.xlsx
+++ b/papertrader/tracker.xlsx
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>470</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
